--- a/NFL/Monday Margins_PlusPlayoffs FF2024.xlsx
+++ b/NFL/Monday Margins_PlusPlayoffs FF2024.xlsx
@@ -8,7 +8,6 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Personal\Stats Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE68AB72-D737-42F2-98B8-216D80E58D34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14850" yWindow="-16320" windowWidth="29040" windowHeight="15840" firstSheet="7" activeTab="16" xr2:uid="{6E320645-5FB5-41FE-86F6-15AD9DF0DED9}"/>
   </bookViews>
@@ -8107,4 +8106,10 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{b1b86c14-7a6f-495c-8ad3-202986669410}" enabled="1" method="Standard" siteId="{2596038f-3ea4-4f0c-aed1-066eb6544c3b}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>